--- a/AlgoTest_Tracker_Clean.xlsx
+++ b/AlgoTest_Tracker_Clean.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -27,23 +27,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
@@ -51,7 +35,6 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <i val="1"/>
       <color rgb="FF5A6A8A"/>
       <sz val="10"/>
@@ -59,7 +42,6 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -67,7 +49,6 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FF2E5090"/>
       <sz val="10"/>
@@ -75,21 +56,18 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <color rgb="FF4A5568"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <sz val="9"/>
     </font>
     <font>
@@ -99,11 +77,35 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="004A5568"/>
+      <color rgb="FF4A5568"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF2E5090"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF4A5568"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -158,12 +160,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,29 +226,9 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
       <bottom style="medium">
         <color rgb="FF2E5090"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -275,133 +257,179 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="52">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -460,47 +488,55 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2E5090"/>
       <rgbColor rgb="FF1B2A4A"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -508,12 +544,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -542,7 +578,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -563,7 +599,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -614,7 +650,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -632,315 +668,465 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" style="12" min="1" max="1"/>
-    <col width="20" customWidth="1" style="12" min="2" max="2"/>
-    <col width="60" customWidth="1" style="12" min="3" max="3"/>
-    <col width="28" customWidth="1" style="12" min="4" max="6"/>
+    <col width="38" customWidth="1" style="39" min="1" max="1"/>
+    <col width="20" customWidth="1" style="39" min="2" max="2"/>
+    <col width="60" customWidth="1" style="39" min="3" max="3"/>
+    <col width="28" customWidth="1" style="39" min="4" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="13">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="27.75" customHeight="1" s="39">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>AlgoTest Options Backtesting — Feature Verification Tracker</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="13">
-      <c r="A2" s="15" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="39">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Research &amp; Verification Sheet  |  Verification columns are blank — for analyst use only</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="13">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="3" ht="21.75" customHeight="1" s="39">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Feature Name</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>V1 Comments</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>V2 Comments</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>V3 Comments</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="13">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="39">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  STRATEGY CONFIG</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n"/>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-    </row>
-    <row r="5" ht="48" customHeight="1" s="13">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="B4" s="42" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+    </row>
+    <row r="5" ht="48" customHeight="1" s="39">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Expiry Selection</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Strategy Config</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>WEEKLY or MONTHLY expiry series per leg.</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="48" customHeight="1" s="13">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>WEEKLY or MONTHLY expiry series per leg.                                                           NEXT WEEKLY or NEXT MONTHLY expiry series per leg.</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="39">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Entry DTE (Days Before Expiry)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Strategy Config</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Trading days before expiry on which the leg enters. DTE=0 enters on expiry day.</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="48" customHeight="1" s="13">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="39">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Exit DTE (Days Before Expiry)</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Strategy Config</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Trading days before expiry on which the leg exits. DTE=0 exits on expiry day.</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="13">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="39">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  LEG BUILDER</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9" ht="48" customHeight="1" s="13">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="B8" s="42" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="42" t="n"/>
+      <c r="F8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="39">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Option Type (CE / PE)</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Leg Builder</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Selects Call or Put for the leg.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="48" customHeight="1" s="13">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="39">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Position Direction (Buy / Sell)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Leg Builder</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Long (Buy) or Short (Sell) position.</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" s="13">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="39">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Segment (Options / Futures)</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Leg Builder</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Options leg or Futures leg.</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-    </row>
-    <row r="12" ht="48" customHeight="1" s="13">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="39">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Strike Type (ATM / OTM 1–20 / ITM 1–20)</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Leg Builder</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Moneyness of the strike — ATM, or N strikes OTM/ITM (1 to 20 strikes from ATM).</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-    </row>
-    <row r="13" ht="48" customHeight="1" s="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="39" thickBot="1">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  INDEX SUPPORT</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" s="13">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="39">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>NIFTY</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="39">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t>Index Selector Groups</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>Index Support</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Only supported index. Strike interval: 50 pts.</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="48" customHeight="1" s="13">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>UI groups indices by expiry availability: Weekly &amp; Monthly (NIFTY, SENSEX) and Monthly Only (MIDCPNIFTY, BANKNIFTY).</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="39">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>Index Support</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>Enabled monthly-only index with monthly / next monthly expiry choices, 100-point strike interval, backend monthly-only validation, and date-aware lot sizing.</t>
+        </is>
+      </c>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="39">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>MIDCPNIFTY</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>Index Support</t>
+        </is>
+      </c>
+      <c r="C17" s="48" t="inlineStr">
+        <is>
+          <t>Enabled monthly-only index with monthly / next monthly expiry choices, 25-point strike interval, backend monthly-only validation, and date-aware lot sizing.</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="39">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>SENSEX</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Index Support</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>Visible in the index selector but blocked from backtesting until option quotes and expiry calendar data are imported.</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="39">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>Index Expiry Guardrails</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Index Support</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="inlineStr">
+        <is>
+          <t>Frontend and backend reject weekly / next weekly expiry selections for monthly-only indices and return clear validation messages.</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="39">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>Centralized Index Metadata</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Index Support</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>Shared service normalizes index symbols, validates configured index support, defines allowed expiries / strike intervals, and supplies historical lot sizes.</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="39">
+      <c r="A21" s="46" t="inlineStr">
+        <is>
+          <t>Re-entry Modes (ASAP / Reverse / Lazy Leg)</t>
+        </is>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="inlineStr">
+        <is>
+          <t>Supports RE ASAP, RE ASAP reverse, RE Momentum, RE Momentum reverse, and Lazy Leg re-entry flows after SL or target triggers. RE_COST is not available.</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="39">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  STRIKE SELECTION</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" s="13">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="39">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>ATM</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="39">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>OTM (Strike Count)</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Strike = round(spot / 50) × 50.</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-    </row>
-    <row r="17" ht="48" customHeight="1" s="13">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>OTM (Strike Count)</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Strike Selection</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Select 1–20 strikes OTM from ATM.
 • CE OTM N: ATM + (N × 50)
@@ -948,22 +1134,26 @@
 Example: NIFTY spot=24350, ATM=24350, OTM2 CE → 24450</t>
         </is>
       </c>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="48" customHeight="1" s="13">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="39">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>ITM (Strike Count)</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Select 1–20 strikes ITM from ATM.
 • CE ITM N: ATM − (N × 50)
@@ -971,417 +1161,421 @@
 Example: NIFTY spot=24350, ATM=24350, ITM2 CE → 24250</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-    </row>
-    <row r="19" ht="48" customHeight="1" s="13">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="39">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Straddle Width (STR)</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>CE: ATM + (multiplier × ATM straddle premium). PE: ATM − same.</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1" s="13">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="39">
+      <c r="A27" s="45" t="inlineStr">
         <is>
           <t>Closest Premium</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Picks the strike whose market premium is nearest to the target value.</t>
         </is>
       </c>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1" s="13">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="39">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Premium Range (Min–Max)</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>Picks the ATM-closest strike with premium within [min, max]. Skips leg if none qualifies.</t>
         </is>
       </c>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-    </row>
-    <row r="22" ht="48" customHeight="1" s="13">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="39">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Premium GTE (≥)</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>Picks the ATM-closest strike with premium ≥ specified value.</t>
         </is>
       </c>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="48" customHeight="1" s="13">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1" s="39">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Premium LTE (≤)</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>Picks the ATM-closest strike with premium ≤ specified value.</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="48" customHeight="1" s="13">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="39">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>Synthetic Future</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Strike Selection</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Picks the strike where |CE premium − PE premium| is smallest.</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="48" customHeight="1" s="13">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Picks the strike where |CE premium - PE premium| is smallest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1" s="39">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  SPOT ADJUSTMENT</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="48" customHeight="1" s="13">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1" s="39">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Spot Adjustment — Direction</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n"/>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="29" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="13">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1" s="39">
+      <c r="A34" s="51" t="inlineStr">
         <is>
           <t>Spot Adjustment — Threshold</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1" s="39">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Spot Adjustment — Units (% / Points)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Spot Adjustment</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>Minimum spot move from entry required to trigger exit.</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-    </row>
-    <row r="28" ht="48" customHeight="1" s="13">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>Spot Adjustment — Units (% / Points)</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Spot Adjustment</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>Threshold expressed as a percentage of spot or fixed points.</t>
         </is>
       </c>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="48" customHeight="1" s="13">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="39">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  BUFFER STRIKE</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="48" customHeight="1" s="13">
-      <c r="A30" s="19" t="inlineStr">
+    </row>
+    <row r="37" ht="48" customHeight="1" s="39">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>Buffer Strike</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="29" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" s="13">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1" s="39">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>Buffer Apply To (CE / PE / Both)</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="48" customHeight="1" s="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>Buffer Value (% / Points)</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Buffer Strike</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>Which legs receive the buffer shift.</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-    </row>
-    <row r="32" ht="48" customHeight="1" s="13">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>Buffer Value (% / Points)</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>Size of the ATM shift — percentage of ATM or fixed points.</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="35" t="n"/>
+    </row>
+    <row r="40" ht="48" customHeight="1" s="39">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Buffer Position (Above / Below)</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>Buffer Strike</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Size of the ATM shift — percentage of ATM or fixed points.</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="48" customHeight="1" s="13">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Buffer Position (Above / Below)</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>Buffer Strike</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>Whether the buffer pushes the strike above or below ATM.</t>
         </is>
       </c>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-    </row>
-    <row r="34" ht="48" customHeight="1" s="13">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="35" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1" s="39">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  RISK MANAGEMENT</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-    </row>
-    <row r="35" ht="48" customHeight="1" s="13">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="42" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="42" t="n"/>
+      <c r="F41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="48" customHeight="1" s="39">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Overall Stop Loss</t>
         </is>
       </c>
-      <c r="B35" s="28" t="n"/>
-      <c r="C35" s="28" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
-      <c r="F35" s="29" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" s="13">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="30" t="n"/>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="35" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="39">
+      <c r="A43" s="50" t="inlineStr">
         <is>
           <t>Per-Leg Stop Loss</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="31" t="n"/>
+    </row>
+    <row r="44" ht="48" customHeight="1" s="39">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Overall Target</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>Each leg has an independent SL. Modes: pct, points, underlying pts/pct.</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-    </row>
-    <row r="37" ht="48" customHeight="1" s="13">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Overall Target</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>Closes all legs when combined unrealised profit hits the target.</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="n"/>
+      <c r="F44" s="35" t="n"/>
+    </row>
+    <row r="45" ht="48" customHeight="1" s="39">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Trailing Stop Loss (per leg)</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>Closes all legs when combined unrealised profit hits the target.</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-    </row>
-    <row r="38" ht="48" customHeight="1" s="13">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>Trailing Stop Loss (per leg)</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>Risk Management</t>
-        </is>
-      </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>SL that tightens as the leg's P&amp;L improves. Configured as X% move activates, trails by Y%.</t>
         </is>
       </c>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-    </row>
-    <row r="39" ht="48" customHeight="1" s="13">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="n"/>
+      <c r="F45" s="35" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="39">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Square Off Mode
 (Partial / Complete)</t>
         </is>
       </c>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Controls how per-leg stop-loss exits are applied when triggered.
 • Partial: only the triggered leg is squared off; other legs continue
 • Complete: all legs are closed when any one leg hits its SL</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="33" t="n"/>
-    </row>
-    <row r="40" ht="48" customHeight="1" s="13">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Front date Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" s="39">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>Re-entry After Stop Loss</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>Re-enters the strategy on the next trading day after a per-leg SL triggers.</t>
         </is>
       </c>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="48" customHeight="1" s="13">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="D47" s="35" t="n"/>
+      <c r="E47" s="35" t="n"/>
+      <c r="F47" s="35" t="n"/>
+    </row>
+    <row r="48" ht="48" customHeight="1" s="39">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>Futures Rollover Exit</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
+      <c r="C48" s="25" t="inlineStr">
         <is>
           <t>Sets when a Futures leg exits relative to contract expiry.
 • ON_EXPIRY: holds to expiry EOD
@@ -1389,191 +1583,191 @@
 • LAST_WEEK_BEFORE_EXPIRY: exits in the last week before expiry</t>
         </is>
       </c>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
-    </row>
-    <row r="42" ht="48" customHeight="1" s="13">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+    </row>
+    <row r="49" ht="48" customHeight="1" s="39">
+      <c r="A49" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARKET FILTER</t>
         </is>
       </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="13">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="B49" s="42" t="n"/>
+      <c r="C49" s="42" t="n"/>
+      <c r="D49" s="42" t="n"/>
+      <c r="E49" s="42" t="n"/>
+      <c r="F49" s="42" t="n"/>
+    </row>
+    <row r="50" ht="48" customHeight="1" s="39">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>SuperTrend Filter (5×1 / 5×2)</t>
         </is>
       </c>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
-      <c r="F43" s="29" t="n"/>
-    </row>
-    <row r="44" ht="48" customHeight="1" s="13">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="B50" s="30" t="n"/>
+      <c r="C50" s="30" t="n"/>
+      <c r="D50" s="30" t="n"/>
+      <c r="E50" s="30" t="n"/>
+      <c r="F50" s="31" t="n"/>
+    </row>
+    <row r="51" ht="48" customHeight="1" s="39">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>Upload Date Range File</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B51" s="33" t="inlineStr">
         <is>
           <t>Market Filter</t>
         </is>
       </c>
-      <c r="C44" s="25" t="inlineStr">
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>Upload a CSV with From/To date pairs. Backtest runs only on dates within those ranges.</t>
         </is>
       </c>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="48" customHeight="1" s="13">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="35" t="n"/>
+    </row>
+    <row r="52" ht="48" customHeight="1" s="39">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  PERFORMANCE METRICS</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1" s="13">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="B52" s="42" t="n"/>
+      <c r="C52" s="42" t="n"/>
+      <c r="D52" s="42" t="n"/>
+      <c r="E52" s="42" t="n"/>
+      <c r="F52" s="42" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>Total P&amp;L (₹ and %)</t>
         </is>
       </c>
-      <c r="B46" s="28" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="29" t="n"/>
-    </row>
-    <row r="47" ht="48" customHeight="1" s="13">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="B53" s="30" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="30" t="n"/>
+      <c r="E53" s="30" t="n"/>
+      <c r="F53" s="31" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>Maximum Drawdown</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C47" s="25" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>Largest peak-to-trough drop in cumulative P&amp;L, shown in ₹ and %.</t>
         </is>
       </c>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="n"/>
-    </row>
-    <row r="48" ht="48" customHeight="1" s="13">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="D54" s="35" t="n"/>
+      <c r="E54" s="35" t="n"/>
+      <c r="F54" s="35" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B55" s="36" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>% of trades that closed with net P&amp;L &gt; 0.</t>
         </is>
       </c>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="22" t="n"/>
-      <c r="F48" s="22" t="n"/>
-    </row>
-    <row r="49" ht="48" customHeight="1" s="13">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="D55" s="35" t="n"/>
+      <c r="E55" s="35" t="n"/>
+      <c r="F55" s="35" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C49" s="25" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>Total winning P&amp;L ÷ |total losing P&amp;L|.</t>
         </is>
       </c>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="22" t="n"/>
-      <c r="F49" s="22" t="n"/>
-    </row>
-    <row r="50" ht="48" customHeight="1" s="13">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="D56" s="35" t="n"/>
+      <c r="E56" s="35" t="n"/>
+      <c r="F56" s="35" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>Monthly P&amp;L Breakdown (Pivot)</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B57" s="36" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>P&amp;L in a Year × Month grid. Trade attributed to exit month.</t>
         </is>
       </c>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
-    </row>
-    <row r="51" ht="48" customHeight="1" s="13">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="D57" s="35" t="n"/>
+      <c r="E57" s="35" t="n"/>
+      <c r="F57" s="35" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>Slippage Simulation</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C51" s="25" t="inlineStr">
+      <c r="C58" s="34" t="inlineStr">
         <is>
           <t>Fixed % applied to every entry and exit to simulate bid-ask spread.</t>
         </is>
       </c>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
-    </row>
-    <row r="52" ht="48" customHeight="1" s="13">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="D58" s="35" t="n"/>
+      <c r="E58" s="35" t="n"/>
+      <c r="F58" s="35" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Transaction Charges
 (Zerodha F&amp;O)</t>
         </is>
       </c>
-      <c r="B52" s="31" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Performance Metrics</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>Applies Zerodha F&amp;O charges to every entry and exit when enabled.
 • Brokerage: ₹20/order
@@ -1584,26 +1778,673 @@
 • GST: 18% on brokerage + txn + SEBI</t>
         </is>
       </c>
-      <c r="D52" s="33" t="n"/>
-      <c r="E52" s="33" t="n"/>
-      <c r="F52" s="33" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C2:R31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" bestFit="1" customWidth="1" style="39" min="18" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="C2" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="H2" t="n">
+        <v>259.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="n">
+        <v>198.85</v>
+      </c>
+      <c r="H3" t="n">
+        <v>198.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4">
+        <f>SUM(C2:C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="n">
+        <v>23750</v>
+      </c>
+      <c r="D6">
+        <f>C6+(C4*1)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>MROUND(D6,50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38</v>
+      </c>
+      <c r="L8" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O8">
+        <f>$N$14-N8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>45665</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="O9">
+        <f>$N$14-N9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>45664</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K10" t="n">
+        <v>149.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>180</v>
+      </c>
+      <c r="M10" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="O10">
+        <f>$N$14-N10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>45663</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K11" t="n">
+        <v>329</v>
+      </c>
+      <c r="L11" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>133.95</v>
+      </c>
+      <c r="O11">
+        <f>$N$14-N11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>45660</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>462.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>480.95</v>
+      </c>
+      <c r="M12" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="O12">
+        <f>$N$14-N12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>45659</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K13" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>527.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>490</v>
+      </c>
+      <c r="O13">
+        <f>$N$14-N13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>45658</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K14" t="n">
+        <v>200.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>302</v>
+      </c>
+      <c r="M14" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>259.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K16" t="n">
+        <v>112</v>
+      </c>
+      <c r="L16" t="n">
+        <v>249.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>112</v>
+      </c>
+      <c r="N16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O16">
+        <f>$N$22-N16</f>
+        <v/>
+      </c>
+      <c r="Q16">
+        <f>O16+O8</f>
+        <v/>
+      </c>
+      <c r="R16">
+        <f>Q16*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>45665</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K17" t="n">
+        <v>142.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>262.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="O17">
+        <f>$N$22-N17</f>
+        <v/>
+      </c>
+      <c r="Q17">
+        <f>O17+O9</f>
+        <v/>
+      </c>
+      <c r="R17">
+        <f>Q17*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>45664</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K18" t="n">
+        <v>312</v>
+      </c>
+      <c r="L18" t="n">
+        <v>312</v>
+      </c>
+      <c r="M18" t="n">
+        <v>113</v>
+      </c>
+      <c r="N18" t="n">
+        <v>142.15</v>
+      </c>
+      <c r="O18">
+        <f>$N$22-N18</f>
+        <v/>
+      </c>
+      <c r="Q18">
+        <f>O18+O10</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>Q18*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>45663</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K19" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>311.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>263.65</v>
+      </c>
+      <c r="O19">
+        <f>$N$22-N19</f>
+        <v/>
+      </c>
+      <c r="Q19">
+        <f>O19+O11</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>Q19*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>45660</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="O20">
+        <f>$N$22-N20</f>
+        <v/>
+      </c>
+      <c r="Q20">
+        <f>O20+O12</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>Q20*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="n">
+        <v>45659</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K21" t="n">
+        <v>193.65</v>
+      </c>
+      <c r="L21" t="n">
+        <v>217</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="O21">
+        <f>$N$22-N21</f>
+        <v/>
+      </c>
+      <c r="Q21">
+        <f>O21+O13</f>
+        <v/>
+      </c>
+      <c r="R21">
+        <f>Q21*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="n">
+        <v>45658</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>45666</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>23750</v>
+      </c>
+      <c r="K22" t="n">
+        <v>240.05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>173</v>
+      </c>
+      <c r="N22" t="n">
+        <v>198.85</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="G28" s="44">
+        <f>F28-(F28*1%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="n">
+        <v>189.35</v>
+      </c>
+      <c r="G29" s="44">
+        <f>F29-(F29*1%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="G30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="F31" t="n">
+        <v>603.3</v>
+      </c>
+      <c r="G31" s="44">
+        <f>F31+(F31*1%)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>